--- a/2025/salida_comparativo_p11/P11_2025_informe_alertas_mes06_vs_mes12.xlsx
+++ b/2025/salida_comparativo_p11/P11_2025_informe_alertas_mes06_vs_mes12.xlsx
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Hospital San Juan de Dios (Santiago)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur - Oriente</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
